--- a/evals/fixtures/annual_schedule_week_fix/annual_schedule.xlsx
+++ b/evals/fixtures/annual_schedule_week_fix/annual_schedule.xlsx
@@ -460,10 +460,26 @@
           <t>第1週4月</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>資材準備2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>打ち合わせ2</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>当日対応2</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>片付け2</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -471,10 +487,26 @@
           <t>第2週4月</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>資材準備3</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>打ち合わせ3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>当日対応3</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>片付け3</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -482,10 +514,26 @@
           <t>第3週4月</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>資材準備4</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>打ち合わせ4</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>当日対応4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>片付け4</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -493,10 +541,26 @@
           <t>第4週4月</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>資材準備5</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>打ち合わせ5</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>当日対応5</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>片付け5</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -509,10 +573,26 @@
           <t>第1週5月</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>資材準備6</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>打ち合わせ6</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>当日対応6</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>片付け6</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -520,10 +600,26 @@
           <t>第2週5月</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>資材準備7</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>打ち合わせ7</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>当日対応7</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>片付け7</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -531,10 +627,26 @@
           <t>第3週5月</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>資材準備8</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>打ち合わせ8</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>当日対応8</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>片付け8</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -542,10 +654,26 @@
           <t>第4週5月</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>資材準備9</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>打ち合わせ9</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>当日対応9</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>片付け9</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -558,10 +686,26 @@
           <t>第1週6月</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>資材準備10</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>打ち合わせ10</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>当日対応10</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>片付け10</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
@@ -569,10 +713,26 @@
           <t>第2週6月</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>資材準備11</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>打ち合わせ11</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>当日対応11</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>片付け11</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -580,10 +740,26 @@
           <t>第3週6月</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>資材準備12</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>打ち合わせ12</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>当日対応12</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>片付け12</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -591,10 +767,26 @@
           <t>第4週6月</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>資材準備13</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>打ち合わせ13</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>当日対応13</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>片付け13</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -607,10 +799,26 @@
           <t>第1週7月</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>資材準備14</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>打ち合わせ14</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>当日対応14</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>片付け14</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
@@ -618,10 +826,26 @@
           <t>第2週7月</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>資材準備15</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>打ち合わせ15</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>当日対応15</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>片付け15</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
@@ -629,10 +853,26 @@
           <t>第3週7月</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>資材準備16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>打ち合わせ16</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>当日対応16</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>片付け16</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
@@ -640,10 +880,26 @@
           <t>第4週7月</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>資材準備17</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>打ち合わせ17</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>当日対応17</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>片付け17</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
@@ -651,10 +907,26 @@
           <t>第1週8月</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>資材準備18</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>打ち合わせ18</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>当日対応18</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>片付け18</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -662,10 +934,26 @@
           <t>第2週8月</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>資材準備19</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>打ち合わせ19</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>当日対応19</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>片付け19</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -678,10 +966,26 @@
           <t>第3週8月</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>資材準備20</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>打ち合わせ20</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>当日対応20</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>片付け20</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
@@ -689,10 +993,26 @@
           <t>第4週8月</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>資材準備21</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>打ち合わせ21</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>当日対応21</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>片付け21</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
@@ -700,10 +1020,26 @@
           <t>第1週9月</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>資材準備22</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>打ち合わせ22</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>当日対応22</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>片付け22</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
@@ -711,10 +1047,26 @@
           <t>第2週9月</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>資材準備23</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>打ち合わせ23</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>当日対応23</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>片付け23</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
@@ -722,10 +1074,26 @@
           <t>第3週9月</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>資材準備24</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>打ち合わせ24</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>当日対応24</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>片付け24</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
@@ -733,10 +1101,26 @@
           <t>第4週9月</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>資材準備25</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>打ち合わせ25</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>当日対応25</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>片付け25</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -749,10 +1133,26 @@
           <t>第1週10月</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>資材準備26</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>打ち合わせ26</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>当日対応26</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>片付け26</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
@@ -760,10 +1160,26 @@
           <t>第2週10月</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>資材準備27</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>打ち合わせ27</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>当日対応27</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>片付け27</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -771,10 +1187,26 @@
           <t>第3週10月</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>資材準備28</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>打ち合わせ28</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>当日対応28</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>片付け28</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
@@ -782,10 +1214,26 @@
           <t>第4週10月</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>資材準備29</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>打ち合わせ29</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>当日対応29</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>片付け29</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
@@ -793,10 +1241,26 @@
           <t>第1週11月</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>資材準備30</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>打ち合わせ30</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>当日対応30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>片付け30</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
@@ -804,10 +1268,26 @@
           <t>第2週11月</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>資材準備31</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>打ち合わせ31</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>当日対応31</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>片付け31</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
@@ -815,10 +1295,26 @@
           <t>第3週11月</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>資材準備32</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>打ち合わせ32</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>当日対応32</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>片付け32</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
@@ -826,10 +1322,26 @@
           <t>第4週11月</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>資材準備33</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>打ち合わせ33</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>当日対応33</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>片付け33</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -842,10 +1354,26 @@
           <t>第1週12月</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>資材準備34</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>打ち合わせ34</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>当日対応34</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>片付け34</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
@@ -853,10 +1381,26 @@
           <t>第2週12月</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>資材準備35</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>打ち合わせ35</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>当日対応35</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>片付け35</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
@@ -864,10 +1408,26 @@
           <t>第3週12月</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>資材準備36</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>打ち合わせ36</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>当日対応36</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>片付け36</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
@@ -875,10 +1435,26 @@
           <t>第4週12月</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>資材準備37</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>打ち合わせ37</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>当日対応37</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>片付け37</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="B38" t="inlineStr">
@@ -886,10 +1462,26 @@
           <t>第1週1月</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>資材準備38</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>打ち合わせ38</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>当日対応38</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>片付け38</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
@@ -897,10 +1489,26 @@
           <t>第2週1月</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>資材準備39</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>打ち合わせ39</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>当日対応39</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>片付け39</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -913,10 +1521,26 @@
           <t>第3週1月</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>資材準備40</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>打ち合わせ40</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>当日対応40</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>片付け40</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
@@ -924,10 +1548,26 @@
           <t>第4週1月</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>資材準備41</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>打ち合わせ41</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>当日対応41</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>片付け41</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="B42" t="inlineStr">
@@ -935,10 +1575,26 @@
           <t>第1週2月</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>資材準備42</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>打ち合わせ42</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>当日対応42</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>片付け42</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
@@ -946,10 +1602,26 @@
           <t>第2週2月</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>資材準備43</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>打ち合わせ43</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>当日対応43</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>片付け43</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
@@ -957,10 +1629,26 @@
           <t>第3週2月</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>資材準備44</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>打ち合わせ44</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>当日対応44</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>片付け44</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
@@ -968,10 +1656,26 @@
           <t>第4週2月</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>資材準備45</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>打ち合わせ45</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>当日対応45</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>片付け45</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -984,10 +1688,26 @@
           <t>第1週3月</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>資材準備46</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>打ち合わせ46</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>当日対応46</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>片付け46</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="B47" t="inlineStr">
@@ -995,10 +1715,26 @@
           <t>第2週3月</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>資材準備47</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>打ち合わせ47</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>当日対応47</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>片付け47</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="B48" t="inlineStr">
@@ -1006,10 +1742,26 @@
           <t>第3週3月</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>資材準備48</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>打ち合わせ48</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>当日対応48</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>片付け48</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="B49" t="inlineStr">
@@ -1017,10 +1769,26 @@
           <t>第4週3月</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>資材準備49</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>打ち合わせ49</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>当日対応49</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>片付け49</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="B50" t="inlineStr">
@@ -1028,10 +1796,26 @@
           <t>第1週4月</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>資材準備50</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>打ち合わせ50</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>当日対応50</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>片付け50</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
@@ -1039,10 +1823,26 @@
           <t>第2週4月</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>資材準備51</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>打ち合わせ51</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>当日対応51</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>片付け51</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="B52" t="inlineStr">
@@ -1050,10 +1850,26 @@
           <t>第3週4月</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>資材準備52</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>打ち合わせ52</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>当日対応52</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>片付け52</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1066,10 +1882,26 @@
           <t>第4週4月</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>資材準備53</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>打ち合わせ53</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>当日対応53</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>片付け53</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="B54" t="inlineStr">
@@ -1077,10 +1909,26 @@
           <t>第1週5月</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>資材準備54</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>打ち合わせ54</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>当日対応54</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>片付け54</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="B55" t="inlineStr">
@@ -1088,10 +1936,26 @@
           <t>第2週5月</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>資材準備55</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>打ち合わせ55</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>当日対応55</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>片付け55</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="B56" t="inlineStr">
@@ -1099,10 +1963,26 @@
           <t>第3週5月</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>資材準備56</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>打ち合わせ56</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>当日対応56</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>片付け56</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="B57" t="inlineStr">
@@ -1110,10 +1990,26 @@
           <t>第4週5月</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>資材準備57</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>打ち合わせ57</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>当日対応57</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>片付け57</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="B58" t="inlineStr">
@@ -1121,10 +2017,26 @@
           <t>第1週6月</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>資材準備58</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>打ち合わせ58</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>当日対応58</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>片付け58</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="B59" t="inlineStr">
@@ -1132,10 +2044,26 @@
           <t>第2週6月</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>資材準備59</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>打ち合わせ59</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>当日対応59</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>片付け59</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1148,10 +2076,26 @@
           <t>第3週6月</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>資材準備60</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>打ち合わせ60</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>当日対応60</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>片付け60</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="B61" t="inlineStr">
@@ -1159,10 +2103,26 @@
           <t>第4週6月</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>資材準備61</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>打ち合わせ61</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>当日対応61</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>片付け61</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="B62" t="inlineStr">
@@ -1170,10 +2130,26 @@
           <t>第1週7月</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>資材準備62</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>打ち合わせ62</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>当日対応62</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>片付け62</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="B63" t="inlineStr">
@@ -1181,10 +2157,26 @@
           <t>第2週7月</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>資材準備63</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>打ち合わせ63</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>当日対応63</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>片付け63</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="B64" t="inlineStr">
@@ -1192,10 +2184,26 @@
           <t>第3週7月</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>資材準備64</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>打ち合わせ64</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>当日対応64</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>片付け64</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="B65" t="inlineStr">
@@ -1203,10 +2211,26 @@
           <t>第4週7月</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>資材準備65</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>打ち合わせ65</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>当日対応65</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>片付け65</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="B66" t="inlineStr">
@@ -1214,10 +2238,26 @@
           <t>第1週8月</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>資材準備66</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>打ち合わせ66</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>当日対応66</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>片付け66</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1230,10 +2270,26 @@
           <t>第2週8月</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>資材準備67</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>打ち合わせ67</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>当日対応67</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>片付け67</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="B68" t="inlineStr">
@@ -1241,10 +2297,26 @@
           <t>第3週8月</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>資材準備68</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>打ち合わせ68</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>当日対応68</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>片付け68</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="B69" t="inlineStr">
@@ -1252,10 +2324,26 @@
           <t>第4週8月</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>資材準備69</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>打ち合わせ69</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>当日対応69</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>片付け69</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="B70" t="inlineStr">
@@ -1263,10 +2351,26 @@
           <t>第1週9月</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>資材準備70</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>打ち合わせ70</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>当日対応70</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>片付け70</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="B71" t="inlineStr">
@@ -1274,10 +2378,26 @@
           <t>第2週9月</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>資材準備71</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>打ち合わせ71</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>当日対応71</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>片付け71</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="B72" t="inlineStr">
@@ -1285,10 +2405,26 @@
           <t>第3週9月</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>資材準備72</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>打ち合わせ72</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>当日対応72</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>片付け72</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="B73" t="inlineStr">
@@ -1296,10 +2432,26 @@
           <t>第4週9月</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>資材準備73</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>打ち合わせ73</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>当日対応73</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>片付け73</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="B74" t="inlineStr">
@@ -1307,10 +2459,26 @@
           <t>第1週10月</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>資材準備74</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>打ち合わせ74</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>当日対応74</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>片付け74</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="B75" t="inlineStr">
@@ -1318,10 +2486,26 @@
           <t>第2週10月</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>資材準備75</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>打ち合わせ75</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>当日対応75</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>片付け75</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="12">
